--- a/database.xlsx
+++ b/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="55">
   <si>
     <t>Nome</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>frango grelhado</t>
+    <t>peito de frango</t>
   </si>
   <si>
     <t>comida</t>
@@ -49,12 +49,15 @@
     <t>alimento</t>
   </si>
   <si>
+    <t>arroz de microondas</t>
+  </si>
+  <si>
+    <t>carboidrato</t>
+  </si>
+  <si>
     <t>arroz integral</t>
   </si>
   <si>
-    <t>carboidrato</t>
-  </si>
-  <si>
     <t>arroz branco</t>
   </si>
   <si>
@@ -64,43 +67,46 @@
     <t>bebida</t>
   </si>
   <si>
+    <t>caminhada</t>
+  </si>
+  <si>
+    <t>exercícios</t>
+  </si>
+  <si>
+    <t>cardio</t>
+  </si>
+  <si>
+    <t>exercício</t>
+  </si>
+  <si>
+    <t>carne bovina moída</t>
+  </si>
+  <si>
+    <t>macarrão</t>
+  </si>
+  <si>
+    <t>chocolate ao leite</t>
+  </si>
+  <si>
+    <t>gordura</t>
+  </si>
+  <si>
+    <t>chocolate 70%</t>
+  </si>
+  <si>
+    <t>amêndoa</t>
+  </si>
+  <si>
+    <t>castanha de caju</t>
+  </si>
+  <si>
+    <t>nozes</t>
+  </si>
+  <si>
+    <t>capuccino</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>caminhada</t>
-  </si>
-  <si>
-    <t>exercícios</t>
-  </si>
-  <si>
-    <t>cardio</t>
-  </si>
-  <si>
-    <t>exercício</t>
-  </si>
-  <si>
-    <t>carne bovina moída</t>
-  </si>
-  <si>
-    <t>macarrão</t>
-  </si>
-  <si>
-    <t>chocolate 70%</t>
-  </si>
-  <si>
-    <t>gordura</t>
-  </si>
-  <si>
-    <t>amêndoa</t>
-  </si>
-  <si>
-    <t>castanha de caju</t>
-  </si>
-  <si>
-    <t>nozes</t>
-  </si>
-  <si>
-    <t>capuccino</t>
   </si>
   <si>
     <t>pão branco</t>
@@ -220,6 +226,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -422,6 +432,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="17.13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -486,16 +499,16 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>124.0</v>
+        <v>152.0</v>
       </c>
       <c r="E3" s="1">
-        <v>1.0</v>
+        <v>2.6</v>
       </c>
       <c r="F3" s="1">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G3" s="1">
-        <v>25.8</v>
+        <v>28.0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>11</v>
@@ -512,16 +525,16 @@
         <v>13</v>
       </c>
       <c r="D4" s="1">
-        <v>130.0</v>
+        <v>124.0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.4</v>
+        <v>1.0</v>
       </c>
       <c r="F4" s="1">
         <v>2.6</v>
       </c>
       <c r="G4" s="1">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>11</v>
@@ -532,22 +545,22 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1">
-        <v>32.0</v>
+        <v>130.0</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="1">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G5" s="1">
-        <v>49.0</v>
+        <v>28.2</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
@@ -555,77 +568,77 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1">
-        <v>5.0</v>
+        <v>32.0</v>
       </c>
       <c r="E6" s="1">
         <v>0.0</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0</v>
+        <v>3.1</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1">
-        <v>250.0</v>
+        <v>5.0</v>
       </c>
       <c r="E7" s="1">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="F7" s="1">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" s="1">
         <v>0.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1">
-        <v>131.0</v>
+        <v>250.0</v>
       </c>
       <c r="E8" s="1">
-        <v>1.1</v>
+        <v>20.0</v>
       </c>
       <c r="F8" s="1">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="G8" s="1">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>11</v>
@@ -633,25 +646,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D9" s="1">
-        <v>598.0</v>
+        <v>131.0</v>
       </c>
       <c r="E9" s="1">
-        <v>42.6</v>
+        <v>1.1</v>
       </c>
       <c r="F9" s="1">
-        <v>7.6</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="1">
-        <v>45.9</v>
+        <v>25.0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>11</v>
@@ -668,16 +681,16 @@
         <v>25</v>
       </c>
       <c r="D10" s="1">
-        <v>535.0</v>
+        <v>598.0</v>
       </c>
       <c r="E10" s="1">
-        <v>29.7</v>
+        <v>42.6</v>
       </c>
       <c r="F10" s="1">
         <v>7.6</v>
       </c>
       <c r="G10" s="1">
-        <v>59.4</v>
+        <v>45.9</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>11</v>
@@ -694,16 +707,16 @@
         <v>25</v>
       </c>
       <c r="D11" s="1">
-        <v>576.0</v>
+        <v>535.0</v>
       </c>
       <c r="E11" s="1">
-        <v>49.4</v>
+        <v>29.7</v>
       </c>
       <c r="F11" s="1">
-        <v>21.2</v>
+        <v>7.6</v>
       </c>
       <c r="G11" s="1">
-        <v>21.6</v>
+        <v>59.4</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>11</v>
@@ -720,16 +733,16 @@
         <v>25</v>
       </c>
       <c r="D12" s="1">
-        <v>570.0</v>
+        <v>576.0</v>
       </c>
       <c r="E12" s="1">
-        <v>46.3</v>
+        <v>49.4</v>
       </c>
       <c r="F12" s="1">
-        <v>18.5</v>
+        <v>21.2</v>
       </c>
       <c r="G12" s="1">
-        <v>29.1</v>
+        <v>21.6</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>11</v>
@@ -746,16 +759,16 @@
         <v>25</v>
       </c>
       <c r="D13" s="1">
-        <v>654.0</v>
+        <v>570.0</v>
       </c>
       <c r="E13" s="1">
-        <v>65.2</v>
+        <v>46.3</v>
       </c>
       <c r="F13" s="1">
-        <v>15.2</v>
+        <v>18.5</v>
       </c>
       <c r="G13" s="1">
-        <v>13.7</v>
+        <v>29.1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>11</v>
@@ -766,22 +779,22 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
-        <v>30.0</v>
+        <v>654.0</v>
       </c>
       <c r="E14" s="1">
-        <v>1.0</v>
+        <v>65.2</v>
       </c>
       <c r="F14" s="1">
-        <v>1.0</v>
+        <v>15.2</v>
       </c>
       <c r="G14" s="1">
-        <v>4.0</v>
+        <v>13.7</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>11</v>
@@ -792,22 +805,22 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1">
-        <v>256.0</v>
+        <v>30.0</v>
       </c>
       <c r="E15" s="1">
-        <v>3.2</v>
+        <v>1.0</v>
       </c>
       <c r="F15" s="1">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="1">
-        <v>49.0</v>
+        <v>4.0</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>11</v>
@@ -815,7 +828,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>9</v>
@@ -824,16 +837,16 @@
         <v>13</v>
       </c>
       <c r="D16" s="1">
-        <v>247.0</v>
+        <v>256.0</v>
       </c>
       <c r="E16" s="1">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="F16" s="1">
-        <v>9.6</v>
+        <v>9.0</v>
       </c>
       <c r="G16" s="1">
-        <v>41.4</v>
+        <v>49.0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>11</v>
@@ -841,25 +854,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1">
-        <v>280.0</v>
+        <v>247.0</v>
       </c>
       <c r="E17" s="1">
-        <v>17.0</v>
+        <v>4.2</v>
       </c>
       <c r="F17" s="1">
-        <v>27.0</v>
+        <v>9.6</v>
       </c>
       <c r="G17" s="1">
-        <v>3.1</v>
+        <v>41.4</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>11</v>
@@ -867,7 +880,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
@@ -876,16 +889,16 @@
         <v>10</v>
       </c>
       <c r="D18" s="1">
-        <v>123.0</v>
+        <v>280.0</v>
       </c>
       <c r="E18" s="1">
-        <v>4.1</v>
+        <v>17.0</v>
       </c>
       <c r="F18" s="1">
-        <v>20.9</v>
+        <v>27.0</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0</v>
+        <v>3.1</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>11</v>
@@ -893,7 +906,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -902,16 +915,16 @@
         <v>10</v>
       </c>
       <c r="D19" s="1">
-        <v>155.0</v>
+        <v>123.0</v>
       </c>
       <c r="E19" s="1">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
       <c r="F19" s="1">
-        <v>12.6</v>
+        <v>20.9</v>
       </c>
       <c r="G19" s="1">
-        <v>1.1</v>
+        <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>11</v>
@@ -919,25 +932,25 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1">
-        <v>884.0</v>
+        <v>155.0</v>
       </c>
       <c r="E20" s="1">
-        <v>100.0</v>
+        <v>10.6</v>
       </c>
       <c r="F20" s="1">
-        <v>0.0</v>
+        <v>12.6</v>
       </c>
       <c r="G20" s="1">
-        <v>0.0</v>
+        <v>1.1</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>11</v>
@@ -945,25 +958,25 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D21" s="1">
-        <v>350.0</v>
+        <v>884.0</v>
       </c>
       <c r="E21" s="1">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="F21" s="1">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" s="1">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>11</v>
@@ -971,7 +984,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
@@ -980,16 +993,16 @@
         <v>13</v>
       </c>
       <c r="D22" s="1">
-        <v>52.0</v>
+        <v>350.0</v>
       </c>
       <c r="E22" s="1">
-        <v>0.2</v>
+        <v>15.0</v>
       </c>
       <c r="F22" s="1">
-        <v>0.3</v>
+        <v>5.0</v>
       </c>
       <c r="G22" s="1">
-        <v>14.0</v>
+        <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>11</v>
@@ -997,7 +1010,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
@@ -1006,16 +1019,16 @@
         <v>13</v>
       </c>
       <c r="D23" s="1">
-        <v>32.0</v>
+        <v>52.0</v>
       </c>
       <c r="E23" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="1">
         <v>0.3</v>
       </c>
-      <c r="F23" s="1">
-        <v>0.7</v>
-      </c>
       <c r="G23" s="1">
-        <v>7.7</v>
+        <v>14.0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>11</v>
@@ -1023,7 +1036,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>9</v>
@@ -1032,16 +1045,16 @@
         <v>13</v>
       </c>
       <c r="D24" s="1">
-        <v>77.0</v>
+        <v>32.0</v>
       </c>
       <c r="E24" s="1">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F24" s="1">
-        <v>2.0</v>
+        <v>0.7</v>
       </c>
       <c r="G24" s="1">
-        <v>17.0</v>
+        <v>7.7</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>11</v>
@@ -1049,7 +1062,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>9</v>
@@ -1058,16 +1071,16 @@
         <v>13</v>
       </c>
       <c r="D25" s="1">
-        <v>41.0</v>
+        <v>77.0</v>
       </c>
       <c r="E25" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="1">
-        <v>0.9</v>
+        <v>2.0</v>
       </c>
       <c r="G25" s="1">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>11</v>
@@ -1075,7 +1088,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
@@ -1084,16 +1097,16 @@
         <v>13</v>
       </c>
       <c r="D26" s="1">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="E26" s="1">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="F26" s="1">
-        <v>2.0</v>
+        <v>0.9</v>
       </c>
       <c r="G26" s="1">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>11</v>
@@ -1101,25 +1114,25 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D27" s="1">
-        <v>207.0</v>
+        <v>40.0</v>
       </c>
       <c r="E27" s="1">
-        <v>11.0</v>
+        <v>1.5</v>
       </c>
       <c r="F27" s="1">
-        <v>3.5</v>
+        <v>2.0</v>
       </c>
       <c r="G27" s="1">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>11</v>
@@ -1127,25 +1140,25 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1">
-        <v>47.0</v>
+        <v>207.0</v>
       </c>
       <c r="E28" s="1">
-        <v>0.1</v>
+        <v>11.0</v>
       </c>
       <c r="F28" s="1">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="G28" s="1">
-        <v>12.0</v>
+        <v>24.0</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>11</v>
@@ -1153,7 +1166,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
@@ -1162,16 +1175,16 @@
         <v>13</v>
       </c>
       <c r="D29" s="1">
-        <v>116.0</v>
+        <v>47.0</v>
       </c>
       <c r="E29" s="1">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F29" s="1">
-        <v>9.0</v>
+        <v>0.9</v>
       </c>
       <c r="G29" s="1">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>11</v>
@@ -1179,7 +1192,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
@@ -1188,16 +1201,16 @@
         <v>13</v>
       </c>
       <c r="D30" s="1">
-        <v>76.0</v>
+        <v>116.0</v>
       </c>
       <c r="E30" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F30" s="1">
-        <v>4.8</v>
+        <v>9.0</v>
       </c>
       <c r="G30" s="1">
-        <v>13.6</v>
+        <v>20.0</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>11</v>
@@ -1205,7 +1218,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
@@ -1214,16 +1227,16 @@
         <v>13</v>
       </c>
       <c r="D31" s="1">
-        <v>84.0</v>
+        <v>76.0</v>
       </c>
       <c r="E31" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="1">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="G31" s="1">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>11</v>
@@ -1231,7 +1244,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
@@ -1240,16 +1253,16 @@
         <v>13</v>
       </c>
       <c r="D32" s="1">
-        <v>500.0</v>
+        <v>84.0</v>
       </c>
       <c r="E32" s="1">
-        <v>25.0</v>
+        <v>0.4</v>
       </c>
       <c r="F32" s="1">
-        <v>6.0</v>
+        <v>5.4</v>
       </c>
       <c r="G32" s="1">
-        <v>62.0</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>11</v>
@@ -1257,7 +1270,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
@@ -1266,16 +1279,16 @@
         <v>13</v>
       </c>
       <c r="D33" s="1">
-        <v>536.0</v>
+        <v>500.0</v>
       </c>
       <c r="E33" s="1">
-        <v>34.6</v>
+        <v>25.0</v>
       </c>
       <c r="F33" s="1">
-        <v>6.5</v>
+        <v>6.0</v>
       </c>
       <c r="G33" s="1">
-        <v>53.0</v>
+        <v>62.0</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>11</v>
@@ -1283,7 +1296,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>9</v>
@@ -1292,16 +1305,16 @@
         <v>13</v>
       </c>
       <c r="D34" s="1">
-        <v>350.0</v>
+        <v>536.0</v>
       </c>
       <c r="E34" s="1">
-        <v>0.0</v>
+        <v>34.6</v>
       </c>
       <c r="F34" s="1">
-        <v>6.0</v>
+        <v>6.5</v>
       </c>
       <c r="G34" s="1">
-        <v>80.0</v>
+        <v>53.0</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>11</v>
@@ -1309,33 +1322,33 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D35" s="1">
-        <v>10.3</v>
+        <v>350.0</v>
       </c>
       <c r="E35" s="1">
         <v>0.0</v>
       </c>
       <c r="F35" s="1">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G35" s="1">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -1344,7 +1357,7 @@
         <v>20</v>
       </c>
       <c r="D36" s="1">
-        <v>8.3</v>
+        <v>10.3</v>
       </c>
       <c r="E36" s="1">
         <v>0.0</v>
@@ -1361,7 +1374,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>19</v>
@@ -1370,18 +1383,44 @@
         <v>20</v>
       </c>
       <c r="D37" s="1">
+        <v>8.3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1">
         <v>6.7</v>
       </c>
-      <c r="E37" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="E38" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="59">
   <si>
     <t>Nome</t>
   </si>
@@ -37,145 +37,157 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>amêndoa</t>
+  </si>
+  <si>
+    <t>comida</t>
+  </si>
+  <si>
+    <t>proteína</t>
+  </si>
+  <si>
+    <t>alimento</t>
+  </si>
+  <si>
+    <t>arroz branco</t>
+  </si>
+  <si>
+    <t>carboidrato</t>
+  </si>
+  <si>
+    <t>arroz de microondas</t>
+  </si>
+  <si>
+    <t>arroz integral</t>
+  </si>
+  <si>
+    <t>azeite de oliva</t>
+  </si>
+  <si>
+    <t>bebida</t>
+  </si>
+  <si>
+    <t>balas de gelatina</t>
+  </si>
+  <si>
+    <t>exercícios</t>
+  </si>
+  <si>
+    <t>cardio</t>
+  </si>
+  <si>
+    <t>exercício</t>
+  </si>
+  <si>
+    <t>batata</t>
+  </si>
+  <si>
+    <t>batata chips</t>
+  </si>
+  <si>
+    <t>bicicleta ergométrica</t>
+  </si>
+  <si>
+    <t>gordura</t>
+  </si>
+  <si>
+    <t>bolo</t>
+  </si>
+  <si>
+    <t>caminhada</t>
+  </si>
+  <si>
+    <t>capuccino</t>
+  </si>
+  <si>
+    <t>carne bovina moída</t>
+  </si>
+  <si>
+    <t>castanha de caju</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>cenoura</t>
+  </si>
+  <si>
+    <t>chocolate 70%</t>
+  </si>
+  <si>
+    <t>chocolate ao leite</t>
+  </si>
+  <si>
+    <t>dança</t>
+  </si>
+  <si>
+    <t>doritos</t>
+  </si>
+  <si>
+    <t>ervilha</t>
+  </si>
+  <si>
+    <t>feijão</t>
+  </si>
+  <si>
+    <t>iogurte de morango</t>
+  </si>
+  <si>
+    <t>iogurte grego</t>
+  </si>
+  <si>
+    <t>iogurte natural 0</t>
+  </si>
+  <si>
+    <t>laranja</t>
+  </si>
+  <si>
+    <t>leite desnatado</t>
+  </si>
+  <si>
+    <t>lentilha</t>
+  </si>
+  <si>
+    <t>maçã</t>
+  </si>
+  <si>
+    <t>macarrão</t>
+  </si>
+  <si>
+    <t>mel</t>
+  </si>
+  <si>
+    <t>morango</t>
+  </si>
+  <si>
+    <t>nozes</t>
+  </si>
+  <si>
+    <t>ovo</t>
+  </si>
+  <si>
+    <t>pão branco</t>
+  </si>
+  <si>
+    <t>pão integral</t>
+  </si>
+  <si>
     <t>peito de frango</t>
   </si>
   <si>
-    <t>comida</t>
-  </si>
-  <si>
-    <t>proteína</t>
-  </si>
-  <si>
-    <t>alimento</t>
-  </si>
-  <si>
-    <t>arroz de microondas</t>
-  </si>
-  <si>
-    <t>carboidrato</t>
-  </si>
-  <si>
-    <t>arroz integral</t>
-  </si>
-  <si>
-    <t>arroz branco</t>
-  </si>
-  <si>
-    <t>leite desnatado</t>
-  </si>
-  <si>
-    <t>bebida</t>
-  </si>
-  <si>
-    <t>caminhada</t>
-  </si>
-  <si>
-    <t>exercícios</t>
-  </si>
-  <si>
-    <t>cardio</t>
-  </si>
-  <si>
-    <t>exercício</t>
-  </si>
-  <si>
-    <t>carne bovina moída</t>
-  </si>
-  <si>
-    <t>macarrão</t>
-  </si>
-  <si>
-    <t>chocolate ao leite</t>
-  </si>
-  <si>
-    <t>gordura</t>
-  </si>
-  <si>
-    <t>chocolate 70%</t>
-  </si>
-  <si>
-    <t>amêndoa</t>
-  </si>
-  <si>
-    <t>castanha de caju</t>
-  </si>
-  <si>
-    <t>nozes</t>
-  </si>
-  <si>
-    <t>capuccino</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>pão branco</t>
-  </si>
-  <si>
-    <t>pão integral</t>
+    <t>presunto</t>
   </si>
   <si>
     <t>queijo mussarela</t>
   </si>
   <si>
-    <t>presunto</t>
-  </si>
-  <si>
-    <t>ovo</t>
-  </si>
-  <si>
-    <t>azeite de oliva</t>
-  </si>
-  <si>
-    <t>bolo</t>
-  </si>
-  <si>
-    <t>maçã</t>
-  </si>
-  <si>
-    <t>morango</t>
-  </si>
-  <si>
-    <t>batata</t>
-  </si>
-  <si>
-    <t>cenoura</t>
-  </si>
-  <si>
     <t>sopa</t>
   </si>
   <si>
     <t>sorvete</t>
   </si>
   <si>
-    <t>laranja</t>
-  </si>
-  <si>
-    <t>lentilha</t>
-  </si>
-  <si>
-    <t>feijão</t>
-  </si>
-  <si>
-    <t>ervilha</t>
-  </si>
-  <si>
-    <t>doritos</t>
-  </si>
-  <si>
-    <t>batata chips</t>
-  </si>
-  <si>
-    <t>balas de gelatina</t>
-  </si>
-  <si>
     <t>subir escadas</t>
-  </si>
-  <si>
-    <t>bicicleta ergométrica</t>
-  </si>
-  <si>
-    <t>dança</t>
   </si>
 </sst>
 </file>
@@ -1019,16 +1031,16 @@
         <v>13</v>
       </c>
       <c r="D23" s="1">
-        <v>52.0</v>
+        <v>45.0</v>
       </c>
       <c r="E23" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="1">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="G23" s="1">
-        <v>14.0</v>
+        <v>5.4</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>11</v>
@@ -1045,16 +1057,16 @@
         <v>13</v>
       </c>
       <c r="D24" s="1">
-        <v>32.0</v>
+        <v>300.0</v>
       </c>
       <c r="E24" s="1">
-        <v>0.3</v>
+        <v>0.0</v>
       </c>
       <c r="F24" s="1">
-        <v>0.7</v>
+        <v>0.0</v>
       </c>
       <c r="G24" s="1">
-        <v>7.7</v>
+        <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>11</v>
@@ -1071,16 +1083,16 @@
         <v>13</v>
       </c>
       <c r="D25" s="1">
-        <v>77.0</v>
+        <v>110.0</v>
       </c>
       <c r="E25" s="1">
-        <v>0.1</v>
+        <v>7.9</v>
       </c>
       <c r="F25" s="1">
-        <v>2.0</v>
+        <v>4.7</v>
       </c>
       <c r="G25" s="1">
-        <v>17.0</v>
+        <v>5.2</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>11</v>
@@ -1097,16 +1109,16 @@
         <v>13</v>
       </c>
       <c r="D26" s="1">
-        <v>41.0</v>
+        <v>62.0</v>
       </c>
       <c r="E26" s="1">
-        <v>0.2</v>
+        <v>1.0</v>
       </c>
       <c r="F26" s="1">
-        <v>0.9</v>
+        <v>11.0</v>
       </c>
       <c r="G26" s="1">
-        <v>10.0</v>
+        <v>2.3</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>11</v>
@@ -1123,16 +1135,16 @@
         <v>13</v>
       </c>
       <c r="D27" s="1">
-        <v>40.0</v>
+        <v>52.0</v>
       </c>
       <c r="E27" s="1">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="F27" s="1">
-        <v>2.0</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="1">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>11</v>
@@ -1146,19 +1158,19 @@
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D28" s="1">
-        <v>207.0</v>
+        <v>32.0</v>
       </c>
       <c r="E28" s="1">
-        <v>11.0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="1">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="G28" s="1">
-        <v>24.0</v>
+        <v>7.7</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>11</v>
@@ -1175,16 +1187,16 @@
         <v>13</v>
       </c>
       <c r="D29" s="1">
-        <v>47.0</v>
+        <v>77.0</v>
       </c>
       <c r="E29" s="1">
         <v>0.1</v>
       </c>
       <c r="F29" s="1">
-        <v>0.9</v>
+        <v>2.0</v>
       </c>
       <c r="G29" s="1">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>11</v>
@@ -1201,16 +1213,16 @@
         <v>13</v>
       </c>
       <c r="D30" s="1">
-        <v>116.0</v>
+        <v>41.0</v>
       </c>
       <c r="E30" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F30" s="1">
-        <v>9.0</v>
+        <v>0.9</v>
       </c>
       <c r="G30" s="1">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>11</v>
@@ -1227,16 +1239,16 @@
         <v>13</v>
       </c>
       <c r="D31" s="1">
-        <v>76.0</v>
+        <v>40.0</v>
       </c>
       <c r="E31" s="1">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F31" s="1">
-        <v>4.8</v>
+        <v>2.0</v>
       </c>
       <c r="G31" s="1">
-        <v>13.6</v>
+        <v>5.0</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>11</v>
@@ -1250,19 +1262,19 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1">
-        <v>84.0</v>
+        <v>207.0</v>
       </c>
       <c r="E32" s="1">
-        <v>0.4</v>
+        <v>11.0</v>
       </c>
       <c r="F32" s="1">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="G32" s="1">
-        <v>14.5</v>
+        <v>24.0</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>11</v>
@@ -1279,16 +1291,16 @@
         <v>13</v>
       </c>
       <c r="D33" s="1">
-        <v>500.0</v>
+        <v>47.0</v>
       </c>
       <c r="E33" s="1">
-        <v>25.0</v>
+        <v>0.1</v>
       </c>
       <c r="F33" s="1">
-        <v>6.0</v>
+        <v>0.9</v>
       </c>
       <c r="G33" s="1">
-        <v>62.0</v>
+        <v>12.0</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>11</v>
@@ -1305,16 +1317,16 @@
         <v>13</v>
       </c>
       <c r="D34" s="1">
-        <v>536.0</v>
+        <v>116.0</v>
       </c>
       <c r="E34" s="1">
-        <v>34.6</v>
+        <v>0.4</v>
       </c>
       <c r="F34" s="1">
-        <v>6.5</v>
+        <v>9.0</v>
       </c>
       <c r="G34" s="1">
-        <v>53.0</v>
+        <v>20.0</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>11</v>
@@ -1331,16 +1343,16 @@
         <v>13</v>
       </c>
       <c r="D35" s="1">
-        <v>350.0</v>
+        <v>76.0</v>
       </c>
       <c r="E35" s="1">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="F35" s="1">
-        <v>6.0</v>
+        <v>4.8</v>
       </c>
       <c r="G35" s="1">
-        <v>80.0</v>
+        <v>13.6</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>11</v>
@@ -1351,25 +1363,25 @@
         <v>52</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D36" s="1">
-        <v>10.3</v>
+        <v>84.0</v>
       </c>
       <c r="E36" s="1">
-        <v>0.0</v>
+        <v>0.4</v>
       </c>
       <c r="F36" s="1">
-        <v>0.0</v>
+        <v>5.4</v>
       </c>
       <c r="G36" s="1">
-        <v>0.0</v>
+        <v>14.5</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1377,25 +1389,25 @@
         <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D37" s="1">
-        <v>8.3</v>
+        <v>500.0</v>
       </c>
       <c r="E37" s="1">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="F37" s="1">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G37" s="1">
-        <v>0.0</v>
+        <v>62.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -1403,24 +1415,128 @@
         <v>54</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1">
+        <v>536.0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>34.6</v>
+      </c>
+      <c r="F38" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1">
+        <v>350.0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D40" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="1">
+        <v>8.3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="1">
         <v>6.7</v>
       </c>
-      <c r="E38" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="E42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="60">
   <si>
     <t>Nome</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>ovo</t>
+  </si>
+  <si>
+    <t>tapioca</t>
   </si>
   <si>
     <t>pão branco</t>
@@ -1343,16 +1346,16 @@
         <v>13</v>
       </c>
       <c r="D35" s="1">
-        <v>76.0</v>
+        <v>242.0</v>
       </c>
       <c r="E35" s="1">
-        <v>0.5</v>
+        <v>60.0</v>
       </c>
       <c r="F35" s="1">
-        <v>4.8</v>
+        <v>0.0</v>
       </c>
       <c r="G35" s="1">
-        <v>13.6</v>
+        <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>11</v>
@@ -1369,16 +1372,16 @@
         <v>13</v>
       </c>
       <c r="D36" s="1">
-        <v>84.0</v>
+        <v>76.0</v>
       </c>
       <c r="E36" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F36" s="1">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="G36" s="1">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>11</v>
@@ -1395,16 +1398,16 @@
         <v>13</v>
       </c>
       <c r="D37" s="1">
-        <v>500.0</v>
+        <v>84.0</v>
       </c>
       <c r="E37" s="1">
-        <v>25.0</v>
+        <v>0.4</v>
       </c>
       <c r="F37" s="1">
-        <v>6.0</v>
+        <v>5.4</v>
       </c>
       <c r="G37" s="1">
-        <v>62.0</v>
+        <v>14.5</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>11</v>
@@ -1421,16 +1424,16 @@
         <v>13</v>
       </c>
       <c r="D38" s="1">
-        <v>536.0</v>
+        <v>500.0</v>
       </c>
       <c r="E38" s="1">
-        <v>34.6</v>
+        <v>25.0</v>
       </c>
       <c r="F38" s="1">
-        <v>6.5</v>
+        <v>6.0</v>
       </c>
       <c r="G38" s="1">
-        <v>53.0</v>
+        <v>62.0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>11</v>
@@ -1447,16 +1450,16 @@
         <v>13</v>
       </c>
       <c r="D39" s="1">
-        <v>350.0</v>
+        <v>536.0</v>
       </c>
       <c r="E39" s="1">
-        <v>0.0</v>
+        <v>34.6</v>
       </c>
       <c r="F39" s="1">
-        <v>6.0</v>
+        <v>6.5</v>
       </c>
       <c r="G39" s="1">
-        <v>80.0</v>
+        <v>53.0</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>11</v>
@@ -1467,25 +1470,25 @@
         <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D40" s="1">
-        <v>10.3</v>
+        <v>350.0</v>
       </c>
       <c r="E40" s="1">
         <v>0.0</v>
       </c>
       <c r="F40" s="1">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G40" s="1">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -1499,7 +1502,7 @@
         <v>20</v>
       </c>
       <c r="D41" s="1">
-        <v>8.3</v>
+        <v>10.3</v>
       </c>
       <c r="E41" s="1">
         <v>0.0</v>
@@ -1525,18 +1528,44 @@
         <v>20</v>
       </c>
       <c r="D42" s="1">
+        <v>8.3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="1">
         <v>6.7</v>
       </c>
-      <c r="E42" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F42" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="E43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
     <t>Nome</t>
   </si>
@@ -37,160 +37,166 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>peito de frango</t>
+  </si>
+  <si>
+    <t>comida</t>
+  </si>
+  <si>
+    <t>proteína</t>
+  </si>
+  <si>
+    <t>alimento</t>
+  </si>
+  <si>
+    <t>arroz de microondas</t>
+  </si>
+  <si>
+    <t>carboidrato</t>
+  </si>
+  <si>
+    <t>arroz integral</t>
+  </si>
+  <si>
+    <t>arroz branco</t>
+  </si>
+  <si>
+    <t>leite desnatado</t>
+  </si>
+  <si>
+    <t>bebida</t>
+  </si>
+  <si>
+    <t>caminhada</t>
+  </si>
+  <si>
+    <t>exercícios</t>
+  </si>
+  <si>
+    <t>cardio</t>
+  </si>
+  <si>
+    <t>exercício</t>
+  </si>
+  <si>
+    <t>carne bovina moída</t>
+  </si>
+  <si>
+    <t>macarrão</t>
+  </si>
+  <si>
+    <t>chocolate ao leite</t>
+  </si>
+  <si>
+    <t>gordura</t>
+  </si>
+  <si>
+    <t>chocolate 70%</t>
+  </si>
+  <si>
     <t>amêndoa</t>
   </si>
   <si>
-    <t>comida</t>
-  </si>
-  <si>
-    <t>proteína</t>
-  </si>
-  <si>
-    <t>alimento</t>
-  </si>
-  <si>
-    <t>arroz branco</t>
-  </si>
-  <si>
-    <t>carboidrato</t>
-  </si>
-  <si>
-    <t>arroz de microondas</t>
-  </si>
-  <si>
-    <t>arroz integral</t>
+    <t>castanha de caju</t>
+  </si>
+  <si>
+    <t>nozes</t>
+  </si>
+  <si>
+    <t>capuccino</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>pão branco</t>
+  </si>
+  <si>
+    <t>pão integral</t>
+  </si>
+  <si>
+    <t>queijo mussarela</t>
+  </si>
+  <si>
+    <t>presunto</t>
+  </si>
+  <si>
+    <t>ovo</t>
   </si>
   <si>
     <t>azeite de oliva</t>
   </si>
   <si>
-    <t>bebida</t>
+    <t>bolo</t>
+  </si>
+  <si>
+    <t>iogurte natural 0</t>
+  </si>
+  <si>
+    <t>mel</t>
+  </si>
+  <si>
+    <t>iogurte grego</t>
+  </si>
+  <si>
+    <t>iogurte de morango</t>
+  </si>
+  <si>
+    <t>maçã</t>
+  </si>
+  <si>
+    <t>morango</t>
+  </si>
+  <si>
+    <t>batata</t>
+  </si>
+  <si>
+    <t>cenoura</t>
+  </si>
+  <si>
+    <t>sopa</t>
+  </si>
+  <si>
+    <t>sorvete</t>
+  </si>
+  <si>
+    <t>laranja</t>
+  </si>
+  <si>
+    <t>lentilha</t>
+  </si>
+  <si>
+    <t>feijão</t>
+  </si>
+  <si>
+    <t>ervilha</t>
+  </si>
+  <si>
+    <t>doritos</t>
+  </si>
+  <si>
+    <t>batata chips</t>
   </si>
   <si>
     <t>balas de gelatina</t>
   </si>
   <si>
-    <t>exercícios</t>
-  </si>
-  <si>
-    <t>cardio</t>
-  </si>
-  <si>
-    <t>exercício</t>
-  </si>
-  <si>
-    <t>batata</t>
-  </si>
-  <si>
-    <t>batata chips</t>
+    <t>subir escadas</t>
   </si>
   <si>
     <t>bicicleta ergométrica</t>
   </si>
   <si>
-    <t>gordura</t>
-  </si>
-  <si>
-    <t>bolo</t>
-  </si>
-  <si>
-    <t>caminhada</t>
-  </si>
-  <si>
-    <t>capuccino</t>
-  </si>
-  <si>
-    <t>carne bovina moída</t>
-  </si>
-  <si>
-    <t>castanha de caju</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>cenoura</t>
-  </si>
-  <si>
-    <t>chocolate 70%</t>
-  </si>
-  <si>
-    <t>chocolate ao leite</t>
-  </si>
-  <si>
     <t>dança</t>
   </si>
   <si>
-    <t>doritos</t>
-  </si>
-  <si>
-    <t>ervilha</t>
-  </si>
-  <si>
-    <t>feijão</t>
-  </si>
-  <si>
-    <t>iogurte de morango</t>
-  </si>
-  <si>
-    <t>iogurte grego</t>
-  </si>
-  <si>
-    <t>iogurte natural 0</t>
-  </si>
-  <si>
-    <t>laranja</t>
-  </si>
-  <si>
-    <t>leite desnatado</t>
-  </si>
-  <si>
-    <t>lentilha</t>
-  </si>
-  <si>
-    <t>maçã</t>
-  </si>
-  <si>
-    <t>macarrão</t>
-  </si>
-  <si>
-    <t>mel</t>
-  </si>
-  <si>
-    <t>morango</t>
-  </si>
-  <si>
-    <t>nozes</t>
-  </si>
-  <si>
-    <t>ovo</t>
-  </si>
-  <si>
     <t>tapioca</t>
   </si>
   <si>
-    <t>pão branco</t>
-  </si>
-  <si>
-    <t>pão integral</t>
-  </si>
-  <si>
-    <t>peito de frango</t>
-  </si>
-  <si>
-    <t>presunto</t>
-  </si>
-  <si>
-    <t>queijo mussarela</t>
-  </si>
-  <si>
-    <t>sopa</t>
-  </si>
-  <si>
-    <t>sorvete</t>
-  </si>
-  <si>
-    <t>subir escadas</t>
+    <t>bolacha de aveia</t>
+  </si>
+  <si>
+    <t>bolacha de sal</t>
   </si>
 </sst>
 </file>
@@ -1346,16 +1352,16 @@
         <v>13</v>
       </c>
       <c r="D35" s="1">
-        <v>242.0</v>
+        <v>76.0</v>
       </c>
       <c r="E35" s="1">
-        <v>60.0</v>
+        <v>0.5</v>
       </c>
       <c r="F35" s="1">
-        <v>0.0</v>
+        <v>4.8</v>
       </c>
       <c r="G35" s="1">
-        <v>0.0</v>
+        <v>13.6</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>11</v>
@@ -1372,16 +1378,16 @@
         <v>13</v>
       </c>
       <c r="D36" s="1">
-        <v>76.0</v>
+        <v>84.0</v>
       </c>
       <c r="E36" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F36" s="1">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="G36" s="1">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>11</v>
@@ -1398,16 +1404,16 @@
         <v>13</v>
       </c>
       <c r="D37" s="1">
-        <v>84.0</v>
+        <v>500.0</v>
       </c>
       <c r="E37" s="1">
-        <v>0.4</v>
+        <v>25.0</v>
       </c>
       <c r="F37" s="1">
-        <v>5.4</v>
+        <v>6.0</v>
       </c>
       <c r="G37" s="1">
-        <v>14.5</v>
+        <v>62.0</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>11</v>
@@ -1424,16 +1430,16 @@
         <v>13</v>
       </c>
       <c r="D38" s="1">
-        <v>500.0</v>
+        <v>536.0</v>
       </c>
       <c r="E38" s="1">
-        <v>25.0</v>
+        <v>34.6</v>
       </c>
       <c r="F38" s="1">
-        <v>6.0</v>
+        <v>6.5</v>
       </c>
       <c r="G38" s="1">
-        <v>62.0</v>
+        <v>53.0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>11</v>
@@ -1450,16 +1456,16 @@
         <v>13</v>
       </c>
       <c r="D39" s="1">
-        <v>536.0</v>
+        <v>350.0</v>
       </c>
       <c r="E39" s="1">
-        <v>34.6</v>
+        <v>0.0</v>
       </c>
       <c r="F39" s="1">
-        <v>6.5</v>
+        <v>6.0</v>
       </c>
       <c r="G39" s="1">
-        <v>53.0</v>
+        <v>80.0</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>11</v>
@@ -1470,25 +1476,25 @@
         <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1">
-        <v>350.0</v>
+        <v>10.3</v>
       </c>
       <c r="E40" s="1">
         <v>0.0</v>
       </c>
       <c r="F40" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" s="1">
-        <v>80.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -1502,7 +1508,7 @@
         <v>20</v>
       </c>
       <c r="D41" s="1">
-        <v>10.3</v>
+        <v>8.3</v>
       </c>
       <c r="E41" s="1">
         <v>0.0</v>
@@ -1528,7 +1534,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="1">
-        <v>8.3</v>
+        <v>6.7</v>
       </c>
       <c r="E42" s="1">
         <v>0.0</v>
@@ -1548,25 +1554,77 @@
         <v>59</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D43" s="1">
+        <v>272.0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="1">
+        <v>495.0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="F44" s="1">
         <v>6.7</v>
       </c>
-      <c r="E43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>21</v>
+      <c r="G44" s="1">
+        <v>60.1</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="1">
+        <v>430.0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="64">
   <si>
     <t>Nome</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t>bolacha de sal</t>
+  </si>
+  <si>
+    <t>corn flakes</t>
+  </si>
+  <si>
+    <t>cereais integrais</t>
   </si>
 </sst>
 </file>
@@ -1627,6 +1633,58 @@
         <v>11</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="1">
+        <v>378.0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="G46" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="1">
+        <v>365.0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F47" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/database.xlsx
+++ b/database.xlsx
@@ -37,295 +37,295 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>Açúcar</t>
+  </si>
+  <si>
+    <t>comida</t>
+  </si>
+  <si>
+    <t>carboidrato</t>
+  </si>
+  <si>
+    <t>alimento</t>
+  </si>
+  <si>
+    <t>Alface</t>
+  </si>
+  <si>
+    <t>Amêndoa</t>
+  </si>
+  <si>
+    <t>proteína</t>
+  </si>
+  <si>
+    <t>Arroz branco</t>
+  </si>
+  <si>
+    <t>Arroz integral</t>
+  </si>
+  <si>
+    <t>Arroz microondas</t>
+  </si>
+  <si>
+    <t>Atum em azeite</t>
+  </si>
+  <si>
+    <t>Aveia</t>
+  </si>
+  <si>
+    <t>Azeite de oliva</t>
+  </si>
+  <si>
+    <t>gordura</t>
+  </si>
+  <si>
+    <t>Bacon</t>
+  </si>
+  <si>
+    <t>Balas de gelatina</t>
+  </si>
+  <si>
+    <t>Batata</t>
+  </si>
+  <si>
+    <t>Batata chips</t>
+  </si>
+  <si>
+    <t>Bicicleta ergométrica</t>
+  </si>
+  <si>
+    <t>exercícios</t>
+  </si>
+  <si>
+    <t>cardio</t>
+  </si>
+  <si>
+    <t>exercício</t>
+  </si>
+  <si>
+    <t>Bolacha de aveia</t>
+  </si>
+  <si>
+    <t>Bolacha de sal</t>
+  </si>
+  <si>
+    <t>Bolo</t>
+  </si>
+  <si>
+    <t>Brócolis</t>
+  </si>
+  <si>
+    <t>Caminhada</t>
+  </si>
+  <si>
+    <t>Cappuccino Dolce Gusto (bebida pronta)</t>
+  </si>
+  <si>
+    <t>bebida</t>
+  </si>
+  <si>
+    <t>Capuccino em pó</t>
+  </si>
+  <si>
+    <t>Carne bovina moída</t>
+  </si>
+  <si>
+    <t>Castanha de caju</t>
+  </si>
+  <si>
+    <t>Cebola</t>
+  </si>
+  <si>
+    <t>Cenoura</t>
+  </si>
+  <si>
+    <t>Cereais integrais</t>
+  </si>
+  <si>
+    <t>Cerejas</t>
+  </si>
+  <si>
+    <t>Chocolate 70%</t>
+  </si>
+  <si>
+    <t>Chocolate ao leite</t>
+  </si>
+  <si>
+    <t>Corn flakes</t>
+  </si>
+  <si>
+    <t>Couve-flor</t>
+  </si>
+  <si>
+    <t>Coxa de frango</t>
+  </si>
+  <si>
+    <t>Dança</t>
+  </si>
+  <si>
+    <t>Doce de leite</t>
+  </si>
+  <si>
+    <t>Doritos</t>
+  </si>
+  <si>
+    <t>Elíptico</t>
+  </si>
+  <si>
+    <t>Ervilha</t>
+  </si>
+  <si>
+    <t>Espinafre</t>
+  </si>
+  <si>
+    <t>Farofa</t>
+  </si>
+  <si>
+    <t>Feijão cozido</t>
+  </si>
+  <si>
+    <t>Flocão de milho</t>
+  </si>
+  <si>
+    <t>Folhado de frango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geleia </t>
+  </si>
+  <si>
+    <t>Gergelim</t>
+  </si>
+  <si>
+    <t>Grão-de-bico cozido</t>
+  </si>
+  <si>
+    <t>Guacamole</t>
+  </si>
+  <si>
+    <t>Iogurte de morango</t>
+  </si>
+  <si>
+    <t>Iogurte grego</t>
+  </si>
+  <si>
+    <t>Iogurte natural 0%</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>Laranja</t>
+  </si>
+  <si>
+    <t>Leite desnatado</t>
+  </si>
+  <si>
+    <t>Leite semidesnatado</t>
+  </si>
+  <si>
+    <t>Lentilha cozida</t>
+  </si>
+  <si>
+    <t>Maçã</t>
+  </si>
+  <si>
+    <t>Macarrão cozido</t>
+  </si>
+  <si>
+    <t>Maionese</t>
+  </si>
+  <si>
+    <t>Manteiga</t>
+  </si>
+  <si>
+    <t>Manteiga de amendoim</t>
+  </si>
+  <si>
+    <t>Marshmallow</t>
+  </si>
+  <si>
+    <t>Mel</t>
+  </si>
+  <si>
+    <t>Melancia</t>
+  </si>
+  <si>
+    <t>Milho em conserva</t>
+  </si>
+  <si>
+    <t>Morango</t>
+  </si>
+  <si>
+    <t>Nozes</t>
+  </si>
+  <si>
+    <t>Ovo</t>
+  </si>
+  <si>
+    <t>Pão branco</t>
+  </si>
+  <si>
+    <t>Pão integral</t>
+  </si>
+  <si>
     <t>Peito de frango</t>
   </si>
   <si>
-    <t>comida</t>
-  </si>
-  <si>
-    <t>proteína</t>
-  </si>
-  <si>
-    <t>alimento</t>
-  </si>
-  <si>
-    <t>Carne bovina moída</t>
+    <t>Peito de peru</t>
+  </si>
+  <si>
+    <t>Pipoca</t>
+  </si>
+  <si>
+    <t>Pizza</t>
   </si>
   <si>
     <t>Presunto</t>
   </si>
   <si>
-    <t>Ovo</t>
+    <t>Queijo de fundir</t>
   </si>
   <si>
     <t>Queijo mussarela</t>
   </si>
   <si>
-    <t>Queijo de fundir</t>
-  </si>
-  <si>
     <t>Queijo ralado</t>
   </si>
   <si>
-    <t>Atum em azeite</t>
-  </si>
-  <si>
-    <t>Bacon</t>
-  </si>
-  <si>
-    <t>Coxa de frango</t>
-  </si>
-  <si>
-    <t>Leite desnatado</t>
-  </si>
-  <si>
-    <t>bebida</t>
-  </si>
-  <si>
-    <t>Leite semidesnatado</t>
-  </si>
-  <si>
-    <t>Iogurte natural 0%</t>
-  </si>
-  <si>
-    <t>Iogurte grego</t>
-  </si>
-  <si>
-    <t>Iogurte de morango</t>
-  </si>
-  <si>
-    <t>Arroz microondas</t>
-  </si>
-  <si>
-    <t>carboidrato</t>
-  </si>
-  <si>
-    <t>Arroz integral</t>
-  </si>
-  <si>
-    <t>Arroz branco</t>
-  </si>
-  <si>
-    <t>Macarrão cozido</t>
-  </si>
-  <si>
-    <t>Pão branco</t>
-  </si>
-  <si>
-    <t>Pão integral</t>
+    <t>Semente de abóbora</t>
+  </si>
+  <si>
+    <t>Semente de girassol</t>
+  </si>
+  <si>
+    <t>Sorvete</t>
+  </si>
+  <si>
+    <t>Subir escadas</t>
+  </si>
+  <si>
+    <t>Suco de laranja</t>
   </si>
   <si>
     <t>Tapioca</t>
   </si>
   <si>
+    <t>Tomate</t>
+  </si>
+  <si>
     <t>Tortilla</t>
   </si>
   <si>
-    <t>Aveia</t>
-  </si>
-  <si>
-    <t>Flocão de milho</t>
-  </si>
-  <si>
-    <t>Corn flakes</t>
-  </si>
-  <si>
-    <t>Cereais integrais</t>
-  </si>
-  <si>
-    <t>Amêndoa</t>
-  </si>
-  <si>
-    <t>Castanha de caju</t>
-  </si>
-  <si>
-    <t>Nozes</t>
+    <t>Tortilla de batata espanhola</t>
   </si>
   <si>
     <t>Trail mix</t>
   </si>
   <si>
-    <t>Semente de girassol</t>
-  </si>
-  <si>
-    <t>gordura</t>
-  </si>
-  <si>
-    <t>Semente de abóbora</t>
-  </si>
-  <si>
-    <t>Gergelim</t>
-  </si>
-  <si>
-    <t>Azeite de oliva</t>
-  </si>
-  <si>
-    <t>Chocolate ao leite</t>
-  </si>
-  <si>
-    <t>Chocolate 70%</t>
-  </si>
-  <si>
-    <t>Capuccino em pó</t>
-  </si>
-  <si>
-    <t>Bolo</t>
-  </si>
-  <si>
-    <t>Sorvete</t>
-  </si>
-  <si>
-    <t>Doritos</t>
-  </si>
-  <si>
-    <t>Batata chips</t>
-  </si>
-  <si>
-    <t>Balas de gelatina</t>
-  </si>
-  <si>
-    <t>Bolacha de aveia</t>
-  </si>
-  <si>
-    <t>Bolacha de sal</t>
-  </si>
-  <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>Pipoca</t>
-  </si>
-  <si>
-    <t>Marshmallow</t>
-  </si>
-  <si>
-    <t>Lentilha cozida</t>
-  </si>
-  <si>
-    <t>Feijão cozido</t>
-  </si>
-  <si>
-    <t>Ervilha</t>
-  </si>
-  <si>
-    <t>Batata</t>
-  </si>
-  <si>
-    <t>Cenoura</t>
-  </si>
-  <si>
-    <t>Tomate</t>
-  </si>
-  <si>
-    <t>Brócolis</t>
-  </si>
-  <si>
-    <t>Espinafre</t>
-  </si>
-  <si>
-    <t>Alface</t>
-  </si>
-  <si>
-    <t>Milho em conserva</t>
-  </si>
-  <si>
-    <t>Farofa</t>
-  </si>
-  <si>
-    <t>Maçã</t>
-  </si>
-  <si>
-    <t>Morango</t>
-  </si>
-  <si>
-    <t>Laranja</t>
-  </si>
-  <si>
-    <t>Kiwi</t>
-  </si>
-  <si>
-    <t>Cerejas</t>
+    <t>Treino aeróbico</t>
   </si>
   <si>
     <t>Uvas</t>
-  </si>
-  <si>
-    <t>Mel</t>
-  </si>
-  <si>
-    <t>Manteiga</t>
-  </si>
-  <si>
-    <t>Açúcar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geleia </t>
-  </si>
-  <si>
-    <t>Manteiga de amendoim</t>
-  </si>
-  <si>
-    <t>Cebola</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
-    <t>Doce de leite</t>
-  </si>
-  <si>
-    <t>Melancia</t>
-  </si>
-  <si>
-    <t>Cappuccino Dolce Gusto (bebida pronta)</t>
-  </si>
-  <si>
-    <t>Tortilla de batata espanhola</t>
-  </si>
-  <si>
-    <t>Peito de peru</t>
-  </si>
-  <si>
-    <t>Maionese</t>
-  </si>
-  <si>
-    <t>Suco de laranja</t>
-  </si>
-  <si>
-    <t>Couve-flor</t>
-  </si>
-  <si>
-    <t>Grão-de-bico cozido</t>
-  </si>
-  <si>
-    <t>Folhado de frango</t>
-  </si>
-  <si>
-    <t>Caminhada</t>
-  </si>
-  <si>
-    <t>exercícios</t>
-  </si>
-  <si>
-    <t>cardio</t>
-  </si>
-  <si>
-    <t>exercício</t>
-  </si>
-  <si>
-    <t>Subir escadas</t>
-  </si>
-  <si>
-    <t>Bicicleta ergométrica</t>
-  </si>
-  <si>
-    <t>Elíptico</t>
-  </si>
-  <si>
-    <t>Dança</t>
-  </si>
-  <si>
-    <t>Treino aeróbico</t>
   </si>
 </sst>
 </file>
@@ -633,16 +633,16 @@
         <v>10</v>
       </c>
       <c r="D2" s="2">
-        <v>165.0</v>
+        <v>400.0</v>
       </c>
       <c r="E2" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="F2" s="2">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="G2" s="2">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>11</v>
@@ -659,16 +659,16 @@
         <v>10</v>
       </c>
       <c r="D3" s="2">
-        <v>250.0</v>
+        <v>15.0</v>
       </c>
       <c r="E3" s="2">
-        <v>15.0</v>
+        <v>0.2</v>
       </c>
       <c r="F3" s="2">
-        <v>26.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>11</v>
@@ -682,19 +682,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>145.0</v>
+        <v>579.0</v>
       </c>
       <c r="E4" s="2">
-        <v>4.0</v>
+        <v>50.0</v>
       </c>
       <c r="F4" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G4" s="2">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>11</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
@@ -711,16 +711,16 @@
         <v>10</v>
       </c>
       <c r="D5" s="2">
-        <v>143.0</v>
+        <v>130.0</v>
       </c>
       <c r="E5" s="2">
-        <v>10.0</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="2">
-        <v>13.0</v>
+        <v>2.7</v>
       </c>
       <c r="G5" s="2">
-        <v>1.0</v>
+        <v>28.0</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -737,16 +737,16 @@
         <v>10</v>
       </c>
       <c r="D6" s="2">
-        <v>280.0</v>
+        <v>112.0</v>
       </c>
       <c r="E6" s="2">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="F6" s="2">
-        <v>22.0</v>
+        <v>2.6</v>
       </c>
       <c r="G6" s="2">
-        <v>3.0</v>
+        <v>23.0</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>11</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -763,16 +763,16 @@
         <v>10</v>
       </c>
       <c r="D7" s="2">
-        <v>290.0</v>
+        <v>130.0</v>
       </c>
       <c r="E7" s="2">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="F7" s="2">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="G7" s="2">
-        <v>7.0</v>
+        <v>28.0</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>11</v>
@@ -780,25 +780,25 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>390.0</v>
+        <v>200.0</v>
       </c>
       <c r="E8" s="2">
-        <v>29.0</v>
+        <v>8.0</v>
       </c>
       <c r="F8" s="2">
-        <v>35.0</v>
+        <v>25.0</v>
       </c>
       <c r="G8" s="2">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>11</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -815,16 +815,16 @@
         <v>10</v>
       </c>
       <c r="D9" s="2">
-        <v>200.0</v>
+        <v>380.0</v>
       </c>
       <c r="E9" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="F9" s="2">
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="G9" s="2">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>11</v>
@@ -832,25 +832,25 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2">
-        <v>500.0</v>
+        <v>884.0</v>
       </c>
       <c r="E10" s="2">
-        <v>42.0</v>
+        <v>100.0</v>
       </c>
       <c r="F10" s="2">
-        <v>37.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>11</v>
@@ -858,25 +858,25 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
-        <v>215.0</v>
+        <v>500.0</v>
       </c>
       <c r="E11" s="2">
-        <v>10.0</v>
+        <v>42.0</v>
       </c>
       <c r="F11" s="2">
-        <v>26.0</v>
+        <v>37.0</v>
       </c>
       <c r="G11" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>11</v>
@@ -884,25 +884,25 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="2">
-        <v>35.0</v>
+        <v>340.0</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2</v>
+        <v>0.0</v>
       </c>
       <c r="F12" s="2">
-        <v>3.4</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="2">
-        <v>5.0</v>
+        <v>77.0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>11</v>
@@ -910,25 +910,25 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="2">
-        <v>50.0</v>
+        <v>77.0</v>
       </c>
       <c r="E13" s="2">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2">
-        <v>3.3</v>
+        <v>2.0</v>
       </c>
       <c r="G13" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>11</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>9</v>
@@ -945,50 +945,50 @@
         <v>10</v>
       </c>
       <c r="D14" s="2">
-        <v>40.0</v>
+        <v>530.0</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2</v>
+        <v>35.0</v>
       </c>
       <c r="F14" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" s="2">
-        <v>5.0</v>
+        <v>53.0</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
+      <c r="A15" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2">
-        <v>95.0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>4.0</v>
+        <v>28</v>
+      </c>
+      <c r="D15" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>9</v>
@@ -997,16 +997,16 @@
         <v>10</v>
       </c>
       <c r="D16" s="2">
-        <v>90.0</v>
+        <v>430.0</v>
       </c>
       <c r="E16" s="2">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="F16" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G16" s="2">
-        <v>15.0</v>
+        <v>69.0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>11</v>
@@ -1014,25 +1014,25 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2">
-        <v>130.0</v>
+        <v>420.0</v>
       </c>
       <c r="E17" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="F17" s="2">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G17" s="2">
-        <v>28.0</v>
+        <v>73.0</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>11</v>
@@ -1040,25 +1040,25 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2">
-        <v>112.0</v>
+        <v>350.0</v>
       </c>
       <c r="E18" s="2">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="F18" s="2">
-        <v>2.6</v>
+        <v>5.0</v>
       </c>
       <c r="G18" s="2">
-        <v>23.0</v>
+        <v>55.0</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>11</v>
@@ -1066,77 +1066,77 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2">
-        <v>130.0</v>
+        <v>34.0</v>
       </c>
       <c r="E19" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F19" s="2">
-        <v>2.7</v>
+        <v>3.0</v>
       </c>
       <c r="G19" s="2">
-        <v>28.0</v>
+        <v>7.0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>31</v>
+      <c r="A20" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="2">
-        <v>150.0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="D20" s="1">
         <v>5.0</v>
       </c>
-      <c r="G20" s="2">
-        <v>30.0</v>
+      <c r="E20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2">
-        <v>265.0</v>
+        <v>60.0</v>
       </c>
       <c r="E21" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F21" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G21" s="2">
-        <v>49.0</v>
+        <v>9.0</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>11</v>
@@ -1144,25 +1144,25 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2">
-        <v>250.0</v>
+        <v>420.0</v>
       </c>
       <c r="E22" s="2">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="F22" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="2">
-        <v>43.0</v>
+        <v>70.0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>11</v>
@@ -1170,25 +1170,25 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2">
-        <v>330.0</v>
+        <v>250.0</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="F23" s="2">
-        <v>0.5</v>
+        <v>26.0</v>
       </c>
       <c r="G23" s="2">
-        <v>87.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>11</v>
@@ -1196,25 +1196,25 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2">
-        <v>300.0</v>
+        <v>553.0</v>
       </c>
       <c r="E24" s="2">
-        <v>7.0</v>
+        <v>44.0</v>
       </c>
       <c r="F24" s="2">
-        <v>8.0</v>
+        <v>18.0</v>
       </c>
       <c r="G24" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>11</v>
@@ -1222,25 +1222,25 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2">
-        <v>380.0</v>
+        <v>40.0</v>
       </c>
       <c r="E25" s="2">
-        <v>7.0</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="2">
-        <v>17.0</v>
+        <v>1.1</v>
       </c>
       <c r="G25" s="2">
-        <v>66.0</v>
+        <v>9.0</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>11</v>
@@ -1248,25 +1248,25 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2">
-        <v>360.0</v>
+        <v>41.0</v>
       </c>
       <c r="E26" s="2">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="F26" s="2">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="2">
-        <v>79.0</v>
+        <v>10.0</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>11</v>
@@ -1274,25 +1274,25 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2">
-        <v>370.0</v>
+        <v>360.0</v>
       </c>
       <c r="E27" s="2">
-        <v>0.4</v>
+        <v>4.0</v>
       </c>
       <c r="F27" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G27" s="2">
-        <v>84.0</v>
+        <v>73.0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>11</v>
@@ -1300,25 +1300,25 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2">
-        <v>360.0</v>
+        <v>63.0</v>
       </c>
       <c r="E28" s="2">
-        <v>4.0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="2">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" s="2">
-        <v>73.0</v>
+        <v>16.0</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>11</v>
@@ -1326,25 +1326,25 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2">
-        <v>579.0</v>
+        <v>510.0</v>
       </c>
       <c r="E29" s="2">
-        <v>50.0</v>
+        <v>43.0</v>
       </c>
       <c r="F29" s="2">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="G29" s="2">
-        <v>22.0</v>
+        <v>46.0</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>11</v>
@@ -1352,25 +1352,25 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2">
-        <v>553.0</v>
+        <v>535.0</v>
       </c>
       <c r="E30" s="2">
-        <v>44.0</v>
+        <v>30.0</v>
       </c>
       <c r="F30" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="G30" s="2">
-        <v>30.0</v>
+        <v>59.0</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>11</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
@@ -1387,16 +1387,16 @@
         <v>10</v>
       </c>
       <c r="D31" s="2">
-        <v>654.0</v>
+        <v>370.0</v>
       </c>
       <c r="E31" s="2">
-        <v>65.0</v>
+        <v>0.4</v>
       </c>
       <c r="F31" s="2">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="G31" s="2">
-        <v>14.0</v>
+        <v>84.0</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>11</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
@@ -1413,16 +1413,16 @@
         <v>10</v>
       </c>
       <c r="D32" s="2">
-        <v>480.0</v>
+        <v>25.0</v>
       </c>
       <c r="E32" s="2">
-        <v>28.0</v>
+        <v>0.3</v>
       </c>
       <c r="F32" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G32" s="2">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>11</v>
@@ -1430,77 +1430,77 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D33" s="2">
-        <v>584.0</v>
+        <v>215.0</v>
       </c>
       <c r="E33" s="2">
-        <v>51.0</v>
+        <v>10.0</v>
       </c>
       <c r="F33" s="2">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="G33" s="2">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>46</v>
+      <c r="A34" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="2">
-        <v>559.0</v>
-      </c>
-      <c r="E34" s="2">
-        <v>49.0</v>
-      </c>
-      <c r="F34" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="G34" s="2">
-        <v>11.0</v>
+        <v>28</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D35" s="2">
-        <v>573.0</v>
+        <v>315.0</v>
       </c>
       <c r="E35" s="2">
-        <v>50.0</v>
+        <v>8.0</v>
       </c>
       <c r="F35" s="2">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="G35" s="2">
-        <v>23.0</v>
+        <v>55.0</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>11</v>
@@ -1508,77 +1508,77 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2">
-        <v>884.0</v>
+        <v>520.0</v>
       </c>
       <c r="E36" s="2">
-        <v>100.0</v>
+        <v>33.0</v>
       </c>
       <c r="F36" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G36" s="2">
-        <v>0.0</v>
+        <v>57.0</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>49</v>
+      <c r="A37" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="2">
-        <v>535.0</v>
-      </c>
-      <c r="E37" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="F37" s="2">
+        <v>28</v>
+      </c>
+      <c r="D37" s="1">
         <v>8.0</v>
       </c>
-      <c r="G37" s="2">
-        <v>59.0</v>
+      <c r="E37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D38" s="2">
-        <v>510.0</v>
+        <v>81.0</v>
       </c>
       <c r="E38" s="2">
-        <v>43.0</v>
+        <v>0.4</v>
       </c>
       <c r="F38" s="2">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="2">
-        <v>46.0</v>
+        <v>14.0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>11</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
@@ -1595,16 +1595,16 @@
         <v>10</v>
       </c>
       <c r="D39" s="2">
-        <v>420.0</v>
+        <v>23.0</v>
       </c>
       <c r="E39" s="2">
-        <v>12.0</v>
+        <v>0.4</v>
       </c>
       <c r="F39" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G39" s="2">
-        <v>70.0</v>
+        <v>4.0</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>11</v>
@@ -1612,25 +1612,25 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2">
-        <v>350.0</v>
+        <v>400.0</v>
       </c>
       <c r="E40" s="2">
         <v>15.0</v>
       </c>
       <c r="F40" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G40" s="2">
-        <v>55.0</v>
+        <v>70.0</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>11</v>
@@ -1638,25 +1638,25 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D41" s="2">
-        <v>207.0</v>
+        <v>127.0</v>
       </c>
       <c r="E41" s="2">
-        <v>11.0</v>
+        <v>0.5</v>
       </c>
       <c r="F41" s="2">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G41" s="2">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>11</v>
@@ -1664,25 +1664,25 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2">
-        <v>520.0</v>
+        <v>360.0</v>
       </c>
       <c r="E42" s="2">
-        <v>33.0</v>
+        <v>1.5</v>
       </c>
       <c r="F42" s="2">
         <v>7.0</v>
       </c>
       <c r="G42" s="2">
-        <v>57.0</v>
+        <v>79.0</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>11</v>
@@ -1690,25 +1690,25 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2">
-        <v>530.0</v>
+        <v>320.0</v>
       </c>
       <c r="E43" s="2">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="F43" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G43" s="2">
-        <v>53.0</v>
+        <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>11</v>
@@ -1716,25 +1716,25 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2">
-        <v>340.0</v>
+        <v>250.0</v>
       </c>
       <c r="E44" s="2">
         <v>0.0</v>
       </c>
       <c r="F44" s="2">
-        <v>5.0</v>
+        <v>0.5</v>
       </c>
       <c r="G44" s="2">
-        <v>77.0</v>
+        <v>65.0</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>11</v>
@@ -1742,25 +1742,25 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2">
-        <v>430.0</v>
+        <v>573.0</v>
       </c>
       <c r="E45" s="2">
-        <v>16.0</v>
+        <v>50.0</v>
       </c>
       <c r="F45" s="2">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="G45" s="2">
-        <v>69.0</v>
+        <v>23.0</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>11</v>
@@ -1768,25 +1768,25 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D46" s="2">
-        <v>420.0</v>
+        <v>164.0</v>
       </c>
       <c r="E46" s="2">
-        <v>12.0</v>
+        <v>2.6</v>
       </c>
       <c r="F46" s="2">
         <v>9.0</v>
       </c>
       <c r="G46" s="2">
-        <v>73.0</v>
+        <v>27.0</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>11</v>
@@ -1794,25 +1794,25 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D47" s="2">
-        <v>266.0</v>
+        <v>160.0</v>
       </c>
       <c r="E47" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="F47" s="2">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G47" s="2">
-        <v>33.0</v>
+        <v>9.0</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>11</v>
@@ -1820,25 +1820,25 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D48" s="2">
-        <v>480.0</v>
+        <v>90.0</v>
       </c>
       <c r="E48" s="2">
-        <v>28.0</v>
+        <v>2.0</v>
       </c>
       <c r="F48" s="2">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G48" s="2">
-        <v>57.0</v>
+        <v>15.0</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>11</v>
@@ -1846,25 +1846,25 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D49" s="2">
-        <v>320.0</v>
+        <v>95.0</v>
       </c>
       <c r="E49" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="F49" s="2">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G49" s="2">
-        <v>81.0</v>
+        <v>4.0</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>11</v>
@@ -1872,25 +1872,25 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D50" s="2">
-        <v>116.0</v>
+        <v>40.0</v>
       </c>
       <c r="E50" s="2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F50" s="2">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G50" s="2">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>11</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>9</v>
@@ -1907,16 +1907,16 @@
         <v>10</v>
       </c>
       <c r="D51" s="2">
-        <v>127.0</v>
+        <v>61.0</v>
       </c>
       <c r="E51" s="2">
         <v>0.5</v>
       </c>
       <c r="F51" s="2">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="G51" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>11</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
@@ -1933,16 +1933,16 @@
         <v>10</v>
       </c>
       <c r="D52" s="2">
-        <v>81.0</v>
+        <v>47.0</v>
       </c>
       <c r="E52" s="2">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F52" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G52" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>11</v>
@@ -1950,25 +1950,25 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D53" s="2">
-        <v>77.0</v>
+        <v>35.0</v>
       </c>
       <c r="E53" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F53" s="2">
-        <v>2.0</v>
+        <v>3.4</v>
       </c>
       <c r="G53" s="2">
-        <v>17.0</v>
+        <v>5.0</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>11</v>
@@ -1976,25 +1976,25 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D54" s="2">
-        <v>41.0</v>
+        <v>50.0</v>
       </c>
       <c r="E54" s="2">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="F54" s="2">
-        <v>1.0</v>
+        <v>3.3</v>
       </c>
       <c r="G54" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>11</v>
@@ -2002,25 +2002,25 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D55" s="2">
-        <v>18.0</v>
+        <v>116.0</v>
       </c>
       <c r="E55" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G55" s="2">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>11</v>
@@ -2028,25 +2028,25 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D56" s="2">
-        <v>34.0</v>
+        <v>52.0</v>
       </c>
       <c r="E56" s="2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F56" s="2">
-        <v>3.0</v>
+        <v>0.3</v>
       </c>
       <c r="G56" s="2">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>11</v>
@@ -2054,25 +2054,25 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D57" s="2">
-        <v>23.0</v>
+        <v>150.0</v>
       </c>
       <c r="E57" s="2">
-        <v>0.4</v>
+        <v>1.0</v>
       </c>
       <c r="F57" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G57" s="2">
-        <v>4.0</v>
+        <v>30.0</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>11</v>
@@ -2080,25 +2080,25 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D58" s="2">
-        <v>15.0</v>
+        <v>680.0</v>
       </c>
       <c r="E58" s="2">
-        <v>0.2</v>
+        <v>75.0</v>
       </c>
       <c r="F58" s="2">
         <v>1.0</v>
       </c>
       <c r="G58" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>11</v>
@@ -2106,25 +2106,25 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D59" s="2">
-        <v>96.0</v>
+        <v>717.0</v>
       </c>
       <c r="E59" s="2">
-        <v>1.5</v>
+        <v>81.0</v>
       </c>
       <c r="F59" s="2">
-        <v>3.0</v>
+        <v>0.5</v>
       </c>
       <c r="G59" s="2">
-        <v>19.0</v>
+        <v>0.5</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>11</v>
@@ -2132,25 +2132,25 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D60" s="2">
-        <v>400.0</v>
+        <v>588.0</v>
       </c>
       <c r="E60" s="2">
-        <v>15.0</v>
+        <v>50.0</v>
       </c>
       <c r="F60" s="2">
-        <v>4.0</v>
+        <v>25.0</v>
       </c>
       <c r="G60" s="2">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>11</v>
@@ -2158,25 +2158,25 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D61" s="2">
-        <v>52.0</v>
+        <v>320.0</v>
       </c>
       <c r="E61" s="2">
-        <v>0.2</v>
+        <v>0.0</v>
       </c>
       <c r="F61" s="2">
-        <v>0.3</v>
+        <v>2.0</v>
       </c>
       <c r="G61" s="2">
-        <v>14.0</v>
+        <v>81.0</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>11</v>
@@ -2184,25 +2184,25 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D62" s="2">
-        <v>32.0</v>
+        <v>304.0</v>
       </c>
       <c r="E62" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F62" s="2">
         <v>0.3</v>
       </c>
-      <c r="F62" s="2">
-        <v>0.7</v>
-      </c>
       <c r="G62" s="2">
-        <v>8.0</v>
+        <v>82.0</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>11</v>
@@ -2210,25 +2210,25 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D63" s="2">
-        <v>47.0</v>
+        <v>30.0</v>
       </c>
       <c r="E63" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F63" s="2">
-        <v>1.0</v>
+        <v>0.6</v>
       </c>
       <c r="G63" s="2">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>11</v>
@@ -2236,25 +2236,25 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D64" s="2">
-        <v>61.0</v>
+        <v>96.0</v>
       </c>
       <c r="E64" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F64" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G64" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>11</v>
@@ -2262,25 +2262,25 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D65" s="2">
-        <v>63.0</v>
+        <v>32.0</v>
       </c>
       <c r="E65" s="2">
         <v>0.3</v>
       </c>
       <c r="F65" s="2">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="G65" s="2">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>11</v>
@@ -2288,25 +2288,25 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D66" s="2">
-        <v>69.0</v>
+        <v>654.0</v>
       </c>
       <c r="E66" s="2">
-        <v>0.2</v>
+        <v>65.0</v>
       </c>
       <c r="F66" s="2">
-        <v>0.7</v>
+        <v>15.0</v>
       </c>
       <c r="G66" s="2">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>11</v>
@@ -2314,25 +2314,25 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D67" s="2">
-        <v>304.0</v>
+        <v>143.0</v>
       </c>
       <c r="E67" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F67" s="2">
-        <v>0.3</v>
+        <v>13.0</v>
       </c>
       <c r="G67" s="2">
-        <v>82.0</v>
+        <v>1.0</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>11</v>
@@ -2340,25 +2340,25 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D68" s="2">
-        <v>717.0</v>
+        <v>265.0</v>
       </c>
       <c r="E68" s="2">
-        <v>81.0</v>
+        <v>3.0</v>
       </c>
       <c r="F68" s="2">
-        <v>0.5</v>
+        <v>8.0</v>
       </c>
       <c r="G68" s="2">
-        <v>0.5</v>
+        <v>49.0</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>11</v>
@@ -2366,25 +2366,25 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D69" s="2">
-        <v>400.0</v>
+        <v>250.0</v>
       </c>
       <c r="E69" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F69" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G69" s="2">
-        <v>100.0</v>
+        <v>43.0</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>11</v>
@@ -2392,25 +2392,25 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D70" s="2">
-        <v>250.0</v>
+        <v>165.0</v>
       </c>
       <c r="E70" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F70" s="2">
-        <v>0.5</v>
+        <v>31.0</v>
       </c>
       <c r="G70" s="2">
-        <v>65.0</v>
+        <v>0.0</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>11</v>
@@ -2418,25 +2418,25 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D71" s="2">
-        <v>588.0</v>
+        <v>105.0</v>
       </c>
       <c r="E71" s="2">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="F71" s="2">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
       <c r="G71" s="2">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>11</v>
@@ -2444,25 +2444,25 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D72" s="2">
-        <v>40.0</v>
+        <v>480.0</v>
       </c>
       <c r="E72" s="2">
-        <v>0.1</v>
+        <v>28.0</v>
       </c>
       <c r="F72" s="2">
-        <v>1.1</v>
+        <v>9.0</v>
       </c>
       <c r="G72" s="2">
-        <v>9.0</v>
+        <v>57.0</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>11</v>
@@ -2470,25 +2470,25 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D73" s="2">
-        <v>160.0</v>
+        <v>266.0</v>
       </c>
       <c r="E73" s="2">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="F73" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="G73" s="2">
-        <v>9.0</v>
+        <v>33.0</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>11</v>
@@ -2496,25 +2496,25 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D74" s="2">
-        <v>315.0</v>
+        <v>145.0</v>
       </c>
       <c r="E74" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="F74" s="2">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="G74" s="2">
-        <v>55.0</v>
+        <v>2.0</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>11</v>
@@ -2522,25 +2522,25 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D75" s="2">
-        <v>30.0</v>
+        <v>290.0</v>
       </c>
       <c r="E75" s="2">
-        <v>0.2</v>
+        <v>24.0</v>
       </c>
       <c r="F75" s="2">
-        <v>0.6</v>
+        <v>16.0</v>
       </c>
       <c r="G75" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>11</v>
@@ -2548,25 +2548,25 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D76" s="2">
-        <v>60.0</v>
+        <v>280.0</v>
       </c>
       <c r="E76" s="2">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="F76" s="2">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="G76" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>11</v>
@@ -2574,25 +2574,25 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D77" s="2">
-        <v>160.0</v>
+        <v>390.0</v>
       </c>
       <c r="E77" s="2">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
       <c r="F77" s="2">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
       <c r="G77" s="2">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>11</v>
@@ -2600,25 +2600,25 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D78" s="2">
-        <v>105.0</v>
+        <v>559.0</v>
       </c>
       <c r="E78" s="2">
-        <v>2.0</v>
+        <v>49.0</v>
       </c>
       <c r="F78" s="2">
-        <v>18.0</v>
+        <v>30.0</v>
       </c>
       <c r="G78" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>11</v>
@@ -2626,25 +2626,25 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D79" s="2">
-        <v>680.0</v>
+        <v>584.0</v>
       </c>
       <c r="E79" s="2">
-        <v>75.0</v>
+        <v>51.0</v>
       </c>
       <c r="F79" s="2">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="G79" s="2">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>11</v>
@@ -2652,77 +2652,77 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D80" s="2">
-        <v>45.0</v>
+        <v>207.0</v>
       </c>
       <c r="E80" s="2">
-        <v>0.2</v>
+        <v>11.0</v>
       </c>
       <c r="F80" s="2">
-        <v>0.7</v>
+        <v>3.0</v>
       </c>
       <c r="G80" s="2">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="s">
-        <v>93</v>
+      <c r="A81" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="E81" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F81" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="G81" s="2">
-        <v>5.0</v>
+      <c r="D81" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="2">
-        <v>164.0</v>
+        <v>45.0</v>
       </c>
       <c r="E82" s="2">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="F82" s="2">
-        <v>9.0</v>
+        <v>0.7</v>
       </c>
       <c r="G82" s="2">
-        <v>27.0</v>
+        <v>10.0</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>11</v>
@@ -2730,132 +2730,132 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D83" s="2">
-        <v>320.0</v>
+        <v>330.0</v>
       </c>
       <c r="E83" s="2">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="F83" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G83" s="2">
+        <v>87.0</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G84" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="E85" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="F85" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="G85" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="2">
+        <v>160.0</v>
+      </c>
+      <c r="E86" s="2">
         <v>10.0</v>
       </c>
-      <c r="G83" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D84" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F84" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D86" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="E86" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F86" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.0</v>
+      <c r="F86" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G86" s="2">
+        <v>12.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D87" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="E87" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0.0</v>
+        <v>14</v>
+      </c>
+      <c r="D87" s="2">
+        <v>480.0</v>
+      </c>
+      <c r="E87" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="F87" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="G87" s="2">
+        <v>50.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -2863,13 +2863,13 @@
         <v>103</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="D88" s="1">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E88" s="1">
         <v>0.0</v>
@@ -2881,33 +2881,33 @@
         <v>0.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D89" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F89" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.0</v>
+        <v>10</v>
+      </c>
+      <c r="D89" s="2">
+        <v>69.0</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="G89" s="2">
+        <v>18.0</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
